--- a/artfynd/A 53456-2023 artfynd.xlsx
+++ b/artfynd/A 53456-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -918,6 +918,582 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>113660931</v>
+      </c>
+      <c r="B4" t="n">
+        <v>77926</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lomtjärnen (Lomtjärnen), Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>502477</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6911601</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>113659639</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56782</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bredmyran (Bredmyran), Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>502004</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6911977</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>113661050</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56927</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lomtjärnen (Lomtjärnen), Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>502517</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6911752</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>113660968</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78173</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lomtjärnen (Lomtjärnen), Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>502513</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6911584</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>113660896</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56004</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lomtjärnen (Lomtjärnen), Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>502372</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6911634</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53456-2023 artfynd.xlsx
+++ b/artfynd/A 53456-2023 artfynd.xlsx
@@ -920,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113660931</v>
+        <v>113659639</v>
       </c>
       <c r="B4" t="n">
-        <v>77926</v>
+        <v>56782</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,35 +936,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lomtjärnen (Lomtjärnen), Mpd</t>
+          <t>Bredmyran (Bredmyran), Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502477</v>
+        <v>502004</v>
       </c>
       <c r="R4" t="n">
-        <v>6911601</v>
+        <v>6911977</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
@@ -1033,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113659639</v>
+        <v>113660931</v>
       </c>
       <c r="B5" t="n">
-        <v>56782</v>
+        <v>77926</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,42 +1056,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bredmyran (Bredmyran), Mpd</t>
+          <t>Lomtjärnen (Lomtjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502004</v>
+        <v>502477</v>
       </c>
       <c r="R5" t="n">
-        <v>6911977</v>
+        <v>6911601</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>

--- a/artfynd/A 53456-2023 artfynd.xlsx
+++ b/artfynd/A 53456-2023 artfynd.xlsx
@@ -920,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113659639</v>
+        <v>113660931</v>
       </c>
       <c r="B4" t="n">
-        <v>56782</v>
+        <v>77954</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,42 +936,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bredmyran (Bredmyran), Mpd</t>
+          <t>Lomtjärnen (Lomtjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502004</v>
+        <v>502477</v>
       </c>
       <c r="R4" t="n">
-        <v>6911977</v>
+        <v>6911601</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
@@ -1040,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113660931</v>
+        <v>113660968</v>
       </c>
       <c r="B5" t="n">
-        <v>77926</v>
+        <v>78201</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,21 +1049,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1081,13 +1074,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502477</v>
+        <v>502513</v>
       </c>
       <c r="R5" t="n">
-        <v>6911601</v>
+        <v>6911584</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1156,7 +1149,7 @@
         <v>113661050</v>
       </c>
       <c r="B6" t="n">
-        <v>56927</v>
+        <v>56955</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1270,10 +1263,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113660968</v>
+        <v>113660896</v>
       </c>
       <c r="B7" t="n">
-        <v>78173</v>
+        <v>56032</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,25 +1275,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1311,13 +1304,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502513</v>
+        <v>502372</v>
       </c>
       <c r="R7" t="n">
-        <v>6911584</v>
+        <v>6911634</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1383,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113660896</v>
+        <v>113659639</v>
       </c>
       <c r="B8" t="n">
-        <v>56004</v>
+        <v>56810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1395,20 +1388,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102613</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1418,16 +1411,23 @@
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lomtjärnen (Lomtjärnen), Mpd</t>
+          <t>Bredmyran (Bredmyran), Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502372</v>
+        <v>502004</v>
       </c>
       <c r="R8" t="n">
-        <v>6911634</v>
+        <v>6911977</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>

--- a/artfynd/A 53456-2023 artfynd.xlsx
+++ b/artfynd/A 53456-2023 artfynd.xlsx
@@ -920,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113660931</v>
+        <v>113660968</v>
       </c>
       <c r="B4" t="n">
-        <v>77954</v>
+        <v>78201</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,21 +936,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502477</v>
+        <v>502513</v>
       </c>
       <c r="R4" t="n">
-        <v>6911601</v>
+        <v>6911584</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1033,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113660968</v>
+        <v>113661050</v>
       </c>
       <c r="B5" t="n">
-        <v>78201</v>
+        <v>56955</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,24 +1049,28 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1074,10 +1078,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502513</v>
+        <v>502517</v>
       </c>
       <c r="R5" t="n">
-        <v>6911584</v>
+        <v>6911752</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1146,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113661050</v>
+        <v>113660931</v>
       </c>
       <c r="B6" t="n">
-        <v>56955</v>
+        <v>77954</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,28 +1166,24 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1191,13 +1191,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502517</v>
+        <v>502477</v>
       </c>
       <c r="R6" t="n">
-        <v>6911752</v>
+        <v>6911601</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 53456-2023 artfynd.xlsx
+++ b/artfynd/A 53456-2023 artfynd.xlsx
@@ -920,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113660968</v>
+        <v>113660931</v>
       </c>
       <c r="B4" t="n">
-        <v>78201</v>
+        <v>77954</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,21 +936,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502513</v>
+        <v>502477</v>
       </c>
       <c r="R4" t="n">
-        <v>6911584</v>
+        <v>6911601</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1033,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113661050</v>
+        <v>113660968</v>
       </c>
       <c r="B5" t="n">
-        <v>56955</v>
+        <v>78201</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,28 +1049,24 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1078,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502517</v>
+        <v>502513</v>
       </c>
       <c r="R5" t="n">
-        <v>6911752</v>
+        <v>6911584</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1150,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113660931</v>
+        <v>113659639</v>
       </c>
       <c r="B6" t="n">
-        <v>77954</v>
+        <v>56810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1166,35 +1162,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lomtjärnen (Lomtjärnen), Mpd</t>
+          <t>Bredmyran (Bredmyran), Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502477</v>
+        <v>502004</v>
       </c>
       <c r="R6" t="n">
-        <v>6911601</v>
+        <v>6911977</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1376,10 +1379,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113659639</v>
+        <v>113661050</v>
       </c>
       <c r="B8" t="n">
-        <v>56810</v>
+        <v>56955</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1392,45 +1395,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bredmyran (Bredmyran), Mpd</t>
+          <t>Lomtjärnen (Lomtjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502004</v>
+        <v>502517</v>
       </c>
       <c r="R8" t="n">
-        <v>6911977</v>
+        <v>6911752</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>

--- a/artfynd/A 53456-2023 artfynd.xlsx
+++ b/artfynd/A 53456-2023 artfynd.xlsx
@@ -920,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113660931</v>
+        <v>113660896</v>
       </c>
       <c r="B4" t="n">
-        <v>77954</v>
+        <v>56032</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,25 +932,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>102613</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502477</v>
+        <v>502372</v>
       </c>
       <c r="R4" t="n">
-        <v>6911601</v>
+        <v>6911634</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113660896</v>
+        <v>113660931</v>
       </c>
       <c r="B7" t="n">
-        <v>56032</v>
+        <v>77954</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,25 +1278,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102613</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502372</v>
+        <v>502477</v>
       </c>
       <c r="R7" t="n">
-        <v>6911634</v>
+        <v>6911601</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>

--- a/artfynd/A 53456-2023 artfynd.xlsx
+++ b/artfynd/A 53456-2023 artfynd.xlsx
@@ -920,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113660896</v>
+        <v>113660931</v>
       </c>
       <c r="B4" t="n">
-        <v>56032</v>
+        <v>77954</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,25 +932,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102613</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502372</v>
+        <v>502477</v>
       </c>
       <c r="R4" t="n">
-        <v>6911634</v>
+        <v>6911601</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
@@ -1033,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113660968</v>
+        <v>113659639</v>
       </c>
       <c r="B5" t="n">
-        <v>78201</v>
+        <v>56810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,38 +1049,45 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lomtjärnen (Lomtjärnen), Mpd</t>
+          <t>Bredmyran (Bredmyran), Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502513</v>
+        <v>502004</v>
       </c>
       <c r="R5" t="n">
-        <v>6911584</v>
+        <v>6911977</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1146,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113659639</v>
+        <v>113660968</v>
       </c>
       <c r="B6" t="n">
-        <v>56810</v>
+        <v>78201</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,45 +1169,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bredmyran (Bredmyran), Mpd</t>
+          <t>Lomtjärnen (Lomtjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502004</v>
+        <v>502513</v>
       </c>
       <c r="R6" t="n">
-        <v>6911977</v>
+        <v>6911584</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113660931</v>
+        <v>113660896</v>
       </c>
       <c r="B7" t="n">
-        <v>77954</v>
+        <v>56032</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,25 +1278,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>102613</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502477</v>
+        <v>502372</v>
       </c>
       <c r="R7" t="n">
-        <v>6911601</v>
+        <v>6911634</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>

--- a/artfynd/A 53456-2023 artfynd.xlsx
+++ b/artfynd/A 53456-2023 artfynd.xlsx
@@ -920,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113660931</v>
+        <v>113661050</v>
       </c>
       <c r="B4" t="n">
-        <v>77954</v>
+        <v>56955</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,24 +936,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -961,13 +965,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502477</v>
+        <v>502517</v>
       </c>
       <c r="R4" t="n">
-        <v>6911601</v>
+        <v>6911752</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1033,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113659639</v>
+        <v>113660896</v>
       </c>
       <c r="B5" t="n">
-        <v>56810</v>
+        <v>56032</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,20 +1049,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>102613</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1068,23 +1072,16 @@
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bredmyran (Bredmyran), Mpd</t>
+          <t>Lomtjärnen (Lomtjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502004</v>
+        <v>502372</v>
       </c>
       <c r="R5" t="n">
-        <v>6911977</v>
+        <v>6911634</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -1153,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113660968</v>
+        <v>113659639</v>
       </c>
       <c r="B6" t="n">
-        <v>78201</v>
+        <v>56810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,38 +1166,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lomtjärnen (Lomtjärnen), Mpd</t>
+          <t>Bredmyran (Bredmyran), Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502513</v>
+        <v>502004</v>
       </c>
       <c r="R6" t="n">
-        <v>6911584</v>
+        <v>6911977</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1266,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113660896</v>
+        <v>113660931</v>
       </c>
       <c r="B7" t="n">
-        <v>56032</v>
+        <v>77954</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,25 +1282,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102613</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1307,10 +1311,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502372</v>
+        <v>502477</v>
       </c>
       <c r="R7" t="n">
-        <v>6911634</v>
+        <v>6911601</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1379,10 +1383,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113661050</v>
+        <v>113660968</v>
       </c>
       <c r="B8" t="n">
-        <v>56955</v>
+        <v>78201</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1395,28 +1399,24 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502517</v>
+        <v>502513</v>
       </c>
       <c r="R8" t="n">
-        <v>6911752</v>
+        <v>6911584</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 53456-2023 artfynd.xlsx
+++ b/artfynd/A 53456-2023 artfynd.xlsx
@@ -920,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113661050</v>
+        <v>113660968</v>
       </c>
       <c r="B4" t="n">
-        <v>56955</v>
+        <v>78201</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,28 +936,24 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -965,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502517</v>
+        <v>502513</v>
       </c>
       <c r="R4" t="n">
-        <v>6911752</v>
+        <v>6911584</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1037,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113660896</v>
+        <v>113660931</v>
       </c>
       <c r="B5" t="n">
-        <v>56032</v>
+        <v>77954</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,25 +1045,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102613</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1078,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502372</v>
+        <v>502477</v>
       </c>
       <c r="R5" t="n">
-        <v>6911634</v>
+        <v>6911601</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -1270,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113660931</v>
+        <v>113660896</v>
       </c>
       <c r="B7" t="n">
-        <v>77954</v>
+        <v>56032</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,25 +1278,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>102613</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1311,10 +1307,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502477</v>
+        <v>502372</v>
       </c>
       <c r="R7" t="n">
-        <v>6911601</v>
+        <v>6911634</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1383,10 +1379,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113660968</v>
+        <v>113661050</v>
       </c>
       <c r="B8" t="n">
-        <v>78201</v>
+        <v>56955</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1399,24 +1395,28 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502513</v>
+        <v>502517</v>
       </c>
       <c r="R8" t="n">
-        <v>6911584</v>
+        <v>6911752</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 53456-2023 artfynd.xlsx
+++ b/artfynd/A 53456-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 53456-2023 artfynd.xlsx
+++ b/artfynd/A 53456-2023 artfynd.xlsx
@@ -1496,7 +1496,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120000048</v>
+        <v>120000078</v>
       </c>
       <c r="B9" t="n">
         <v>78263</v>
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502578</v>
+        <v>502534</v>
       </c>
       <c r="R9" t="n">
-        <v>6911605</v>
+        <v>6911631</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1606,7 +1606,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120000096</v>
+        <v>120000064</v>
       </c>
       <c r="B10" t="n">
         <v>78263</v>
@@ -1644,11 +1644,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1657,10 +1653,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502537</v>
+        <v>502560</v>
       </c>
       <c r="R10" t="n">
-        <v>6911660</v>
+        <v>6911614</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1720,7 +1716,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120000064</v>
+        <v>120000023</v>
       </c>
       <c r="B11" t="n">
         <v>78263</v>
@@ -1767,10 +1763,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502560</v>
+        <v>502651</v>
       </c>
       <c r="R11" t="n">
-        <v>6911614</v>
+        <v>6911576</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1830,10 +1826,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120000128</v>
+        <v>120000096</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>78263</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1842,30 +1838,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1874,7 +1870,6 @@
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1882,10 +1877,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502567</v>
+        <v>502537</v>
       </c>
       <c r="R12" t="n">
-        <v>6911635</v>
+        <v>6911660</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1945,10 +1940,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120000023</v>
+        <v>120000128</v>
       </c>
       <c r="B13" t="n">
-        <v>78263</v>
+        <v>97907</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1957,34 +1952,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502651</v>
+        <v>502567</v>
       </c>
       <c r="R13" t="n">
-        <v>6911576</v>
+        <v>6911635</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120000078</v>
+        <v>120000048</v>
       </c>
       <c r="B14" t="n">
         <v>78263</v>
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>502534</v>
+        <v>502578</v>
       </c>
       <c r="R14" t="n">
-        <v>6911631</v>
+        <v>6911605</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>

--- a/artfynd/A 53456-2023 artfynd.xlsx
+++ b/artfynd/A 53456-2023 artfynd.xlsx
@@ -1496,10 +1496,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120000078</v>
+        <v>120000128</v>
       </c>
       <c r="B9" t="n">
-        <v>78263</v>
+        <v>97907</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1508,34 +1508,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1543,10 +1548,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502534</v>
+        <v>502567</v>
       </c>
       <c r="R9" t="n">
-        <v>6911631</v>
+        <v>6911635</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1606,7 +1611,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120000064</v>
+        <v>120000048</v>
       </c>
       <c r="B10" t="n">
         <v>78263</v>
@@ -1653,10 +1658,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502560</v>
+        <v>502578</v>
       </c>
       <c r="R10" t="n">
-        <v>6911614</v>
+        <v>6911605</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1716,7 +1721,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120000023</v>
+        <v>120000078</v>
       </c>
       <c r="B11" t="n">
         <v>78263</v>
@@ -1763,10 +1768,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502651</v>
+        <v>502534</v>
       </c>
       <c r="R11" t="n">
-        <v>6911576</v>
+        <v>6911631</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1826,7 +1831,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120000096</v>
+        <v>120000064</v>
       </c>
       <c r="B12" t="n">
         <v>78263</v>
@@ -1864,11 +1869,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1877,10 +1878,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502537</v>
+        <v>502560</v>
       </c>
       <c r="R12" t="n">
-        <v>6911660</v>
+        <v>6911614</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1940,10 +1941,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120000128</v>
+        <v>120000023</v>
       </c>
       <c r="B13" t="n">
-        <v>97907</v>
+        <v>78263</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1952,39 +1953,34 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1992,10 +1988,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502567</v>
+        <v>502651</v>
       </c>
       <c r="R13" t="n">
-        <v>6911635</v>
+        <v>6911576</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2055,7 +2051,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120000048</v>
+        <v>120000096</v>
       </c>
       <c r="B14" t="n">
         <v>78263</v>
@@ -2093,7 +2089,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>502578</v>
+        <v>502537</v>
       </c>
       <c r="R14" t="n">
-        <v>6911605</v>
+        <v>6911660</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>

--- a/artfynd/A 53456-2023 artfynd.xlsx
+++ b/artfynd/A 53456-2023 artfynd.xlsx
@@ -1496,10 +1496,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120000128</v>
+        <v>120000048</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
+        <v>78263</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1508,39 +1508,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1548,10 +1543,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502567</v>
+        <v>502578</v>
       </c>
       <c r="R9" t="n">
-        <v>6911635</v>
+        <v>6911605</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1611,7 +1606,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120000048</v>
+        <v>120000023</v>
       </c>
       <c r="B10" t="n">
         <v>78263</v>
@@ -1658,10 +1653,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502578</v>
+        <v>502651</v>
       </c>
       <c r="R10" t="n">
-        <v>6911605</v>
+        <v>6911576</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1721,10 +1716,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120000078</v>
+        <v>120000128</v>
       </c>
       <c r="B11" t="n">
-        <v>78263</v>
+        <v>97907</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1733,34 +1728,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502534</v>
+        <v>502567</v>
       </c>
       <c r="R11" t="n">
-        <v>6911631</v>
+        <v>6911635</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1941,7 +1941,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120000023</v>
+        <v>120000096</v>
       </c>
       <c r="B13" t="n">
         <v>78263</v>
@@ -1979,7 +1979,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -1988,10 +1992,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502651</v>
+        <v>502537</v>
       </c>
       <c r="R13" t="n">
-        <v>6911576</v>
+        <v>6911660</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2051,7 +2055,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120000096</v>
+        <v>120000078</v>
       </c>
       <c r="B14" t="n">
         <v>78263</v>
@@ -2089,11 +2093,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>502537</v>
+        <v>502534</v>
       </c>
       <c r="R14" t="n">
-        <v>6911660</v>
+        <v>6911631</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>

--- a/artfynd/A 53456-2023 artfynd.xlsx
+++ b/artfynd/A 53456-2023 artfynd.xlsx
@@ -1496,10 +1496,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120000048</v>
+        <v>120000023</v>
       </c>
       <c r="B9" t="n">
-        <v>78263</v>
+        <v>78279</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502578</v>
+        <v>502651</v>
       </c>
       <c r="R9" t="n">
-        <v>6911605</v>
+        <v>6911576</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1606,10 +1606,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120000023</v>
+        <v>120000048</v>
       </c>
       <c r="B10" t="n">
-        <v>78263</v>
+        <v>78279</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502651</v>
+        <v>502578</v>
       </c>
       <c r="R10" t="n">
-        <v>6911576</v>
+        <v>6911605</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1716,10 +1716,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120000128</v>
+        <v>120000078</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>78279</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,39 +1728,34 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1768,10 +1763,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502567</v>
+        <v>502534</v>
       </c>
       <c r="R11" t="n">
-        <v>6911635</v>
+        <v>6911631</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1834,7 +1829,7 @@
         <v>120000064</v>
       </c>
       <c r="B12" t="n">
-        <v>78263</v>
+        <v>78279</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1941,10 +1936,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120000096</v>
+        <v>120000128</v>
       </c>
       <c r="B13" t="n">
-        <v>78263</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1953,30 +1948,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1985,6 +1980,7 @@
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1992,10 +1988,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502537</v>
+        <v>502567</v>
       </c>
       <c r="R13" t="n">
-        <v>6911660</v>
+        <v>6911635</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2055,10 +2051,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120000078</v>
+        <v>120000096</v>
       </c>
       <c r="B14" t="n">
-        <v>78263</v>
+        <v>78279</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2093,7 +2089,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>502534</v>
+        <v>502537</v>
       </c>
       <c r="R14" t="n">
-        <v>6911631</v>
+        <v>6911660</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>

--- a/artfynd/A 53456-2023 artfynd.xlsx
+++ b/artfynd/A 53456-2023 artfynd.xlsx
@@ -1496,7 +1496,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120000023</v>
+        <v>120000048</v>
       </c>
       <c r="B9" t="n">
         <v>78279</v>
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502651</v>
+        <v>502578</v>
       </c>
       <c r="R9" t="n">
-        <v>6911576</v>
+        <v>6911605</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1606,7 +1606,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120000048</v>
+        <v>120000023</v>
       </c>
       <c r="B10" t="n">
         <v>78279</v>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502578</v>
+        <v>502651</v>
       </c>
       <c r="R10" t="n">
-        <v>6911605</v>
+        <v>6911576</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1716,10 +1716,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120000078</v>
+        <v>120000128</v>
       </c>
       <c r="B11" t="n">
-        <v>78279</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,34 +1728,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1763,10 +1768,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502534</v>
+        <v>502567</v>
       </c>
       <c r="R11" t="n">
-        <v>6911631</v>
+        <v>6911635</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1826,7 +1831,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120000064</v>
+        <v>120000078</v>
       </c>
       <c r="B12" t="n">
         <v>78279</v>
@@ -1873,10 +1878,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502560</v>
+        <v>502534</v>
       </c>
       <c r="R12" t="n">
-        <v>6911614</v>
+        <v>6911631</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1936,10 +1941,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120000128</v>
+        <v>120000064</v>
       </c>
       <c r="B13" t="n">
-        <v>97930</v>
+        <v>78279</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1948,39 +1953,34 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502567</v>
+        <v>502560</v>
       </c>
       <c r="R13" t="n">
-        <v>6911635</v>
+        <v>6911614</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 53456-2023 artfynd.xlsx
+++ b/artfynd/A 53456-2023 artfynd.xlsx
@@ -1831,7 +1831,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120000078</v>
+        <v>120000064</v>
       </c>
       <c r="B12" t="n">
         <v>78279</v>
@@ -1878,10 +1878,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502534</v>
+        <v>502560</v>
       </c>
       <c r="R12" t="n">
-        <v>6911631</v>
+        <v>6911614</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1941,7 +1941,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120000064</v>
+        <v>120000096</v>
       </c>
       <c r="B13" t="n">
         <v>78279</v>
@@ -1979,7 +1979,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -1988,10 +1992,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502560</v>
+        <v>502537</v>
       </c>
       <c r="R13" t="n">
-        <v>6911614</v>
+        <v>6911660</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2051,7 +2055,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120000096</v>
+        <v>120000078</v>
       </c>
       <c r="B14" t="n">
         <v>78279</v>
@@ -2089,11 +2093,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>502537</v>
+        <v>502534</v>
       </c>
       <c r="R14" t="n">
-        <v>6911660</v>
+        <v>6911631</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>

--- a/artfynd/A 53456-2023 artfynd.xlsx
+++ b/artfynd/A 53456-2023 artfynd.xlsx
@@ -1496,7 +1496,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120000048</v>
+        <v>120000023</v>
       </c>
       <c r="B9" t="n">
         <v>78279</v>
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502578</v>
+        <v>502651</v>
       </c>
       <c r="R9" t="n">
-        <v>6911605</v>
+        <v>6911576</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1606,7 +1606,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120000023</v>
+        <v>120000064</v>
       </c>
       <c r="B10" t="n">
         <v>78279</v>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502651</v>
+        <v>502560</v>
       </c>
       <c r="R10" t="n">
-        <v>6911576</v>
+        <v>6911614</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1716,10 +1716,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120000128</v>
+        <v>120000078</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
+        <v>78279</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,39 +1728,34 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1768,10 +1763,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502567</v>
+        <v>502534</v>
       </c>
       <c r="R11" t="n">
-        <v>6911635</v>
+        <v>6911631</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1831,7 +1826,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120000064</v>
+        <v>120000048</v>
       </c>
       <c r="B12" t="n">
         <v>78279</v>
@@ -1878,10 +1873,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502560</v>
+        <v>502578</v>
       </c>
       <c r="R12" t="n">
-        <v>6911614</v>
+        <v>6911605</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2055,10 +2050,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120000078</v>
+        <v>120000128</v>
       </c>
       <c r="B14" t="n">
-        <v>78279</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2067,34 +2062,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>502534</v>
+        <v>502567</v>
       </c>
       <c r="R14" t="n">
-        <v>6911631</v>
+        <v>6911635</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>

--- a/artfynd/A 53456-2023 artfynd.xlsx
+++ b/artfynd/A 53456-2023 artfynd.xlsx
@@ -1496,7 +1496,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120000023</v>
+        <v>120000064</v>
       </c>
       <c r="B9" t="n">
         <v>78279</v>
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502651</v>
+        <v>502560</v>
       </c>
       <c r="R9" t="n">
-        <v>6911576</v>
+        <v>6911614</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1606,7 +1606,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120000064</v>
+        <v>120000023</v>
       </c>
       <c r="B10" t="n">
         <v>78279</v>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502560</v>
+        <v>502651</v>
       </c>
       <c r="R10" t="n">
-        <v>6911614</v>
+        <v>6911576</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1716,7 +1716,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120000078</v>
+        <v>120000096</v>
       </c>
       <c r="B11" t="n">
         <v>78279</v>
@@ -1754,7 +1754,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1763,10 +1767,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502534</v>
+        <v>502537</v>
       </c>
       <c r="R11" t="n">
-        <v>6911631</v>
+        <v>6911660</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1936,7 +1940,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120000096</v>
+        <v>120000078</v>
       </c>
       <c r="B13" t="n">
         <v>78279</v>
@@ -1974,11 +1978,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502537</v>
+        <v>502534</v>
       </c>
       <c r="R13" t="n">
-        <v>6911660</v>
+        <v>6911631</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 53456-2023 artfynd.xlsx
+++ b/artfynd/A 53456-2023 artfynd.xlsx
@@ -1496,7 +1496,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120000064</v>
+        <v>120000023</v>
       </c>
       <c r="B9" t="n">
         <v>78279</v>
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502560</v>
+        <v>502651</v>
       </c>
       <c r="R9" t="n">
-        <v>6911614</v>
+        <v>6911576</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1606,7 +1606,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120000023</v>
+        <v>120000078</v>
       </c>
       <c r="B10" t="n">
         <v>78279</v>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502651</v>
+        <v>502534</v>
       </c>
       <c r="R10" t="n">
-        <v>6911576</v>
+        <v>6911631</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1716,7 +1716,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120000096</v>
+        <v>120000064</v>
       </c>
       <c r="B11" t="n">
         <v>78279</v>
@@ -1754,11 +1754,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1767,10 +1763,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502537</v>
+        <v>502560</v>
       </c>
       <c r="R11" t="n">
-        <v>6911660</v>
+        <v>6911614</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1940,7 +1936,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120000078</v>
+        <v>120000096</v>
       </c>
       <c r="B13" t="n">
         <v>78279</v>
@@ -1978,7 +1974,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502534</v>
+        <v>502537</v>
       </c>
       <c r="R13" t="n">
-        <v>6911631</v>
+        <v>6911660</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 53456-2023 artfynd.xlsx
+++ b/artfynd/A 53456-2023 artfynd.xlsx
@@ -1496,10 +1496,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120000023</v>
+        <v>120000128</v>
       </c>
       <c r="B9" t="n">
-        <v>78279</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1508,34 +1508,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1543,10 +1548,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502651</v>
+        <v>502567</v>
       </c>
       <c r="R9" t="n">
-        <v>6911576</v>
+        <v>6911635</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1606,7 +1611,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120000078</v>
+        <v>120000064</v>
       </c>
       <c r="B10" t="n">
         <v>78279</v>
@@ -1653,10 +1658,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502534</v>
+        <v>502560</v>
       </c>
       <c r="R10" t="n">
-        <v>6911631</v>
+        <v>6911614</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1716,7 +1721,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120000064</v>
+        <v>120000023</v>
       </c>
       <c r="B11" t="n">
         <v>78279</v>
@@ -1763,10 +1768,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502560</v>
+        <v>502651</v>
       </c>
       <c r="R11" t="n">
-        <v>6911614</v>
+        <v>6911576</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1826,7 +1831,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120000048</v>
+        <v>120000078</v>
       </c>
       <c r="B12" t="n">
         <v>78279</v>
@@ -1873,10 +1878,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502578</v>
+        <v>502534</v>
       </c>
       <c r="R12" t="n">
-        <v>6911605</v>
+        <v>6911631</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2050,10 +2055,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120000128</v>
+        <v>120000048</v>
       </c>
       <c r="B14" t="n">
-        <v>97930</v>
+        <v>78279</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2062,39 +2067,34 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>502567</v>
+        <v>502578</v>
       </c>
       <c r="R14" t="n">
-        <v>6911635</v>
+        <v>6911605</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>

--- a/artfynd/A 53456-2023 artfynd.xlsx
+++ b/artfynd/A 53456-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,14 +798,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101076821</v>
+        <v>99037590</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
+        <v>98197</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -833,28 +833,30 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rörmyrberget , Mpd</t>
+          <t>Lomtjärn, 300 m V om, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502521.7366323246</v>
+        <v>502568</v>
       </c>
       <c r="R3" t="n">
-        <v>6911808.340592482</v>
+        <v>6911690</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,24 +878,19 @@
           <t>Haverö</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Y-Ång-0116</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-05-23</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-05-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,28 +899,38 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Agneta Toomingas</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113660896</v>
+        <v>101076821</v>
       </c>
       <c r="B4" t="n">
-        <v>56481</v>
+        <v>96334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,42 +939,51 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102613</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lomtjärnen (Lomtjärnen), Mpd</t>
+          <t>Rörmyrberget , Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502372</v>
+        <v>502521.7366323246</v>
       </c>
       <c r="R4" t="n">
-        <v>6911633</v>
+        <v>6911808.340592482</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,22 +1007,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2022-05-23</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2022-05-23</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,22 +1037,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113660968</v>
+        <v>113660896</v>
       </c>
       <c r="B5" t="n">
-        <v>78507</v>
+        <v>56481</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,25 +1061,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1074,13 +1090,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502513</v>
+        <v>502372</v>
       </c>
       <c r="R5" t="n">
-        <v>6911584</v>
+        <v>6911633</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1146,10 +1162,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113659639</v>
+        <v>113660968</v>
       </c>
       <c r="B6" t="n">
-        <v>57265</v>
+        <v>78507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,45 +1178,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bredmyran (Bredmyran), Mpd</t>
+          <t>Lomtjärnen (Lomtjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502004</v>
+        <v>502513</v>
       </c>
       <c r="R6" t="n">
-        <v>6911976</v>
+        <v>6911584</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1266,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113661050</v>
+        <v>113659639</v>
       </c>
       <c r="B7" t="n">
-        <v>57414</v>
+        <v>57265</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,42 +1291,45 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lomtjärnen (Lomtjärnen), Mpd</t>
+          <t>Bredmyran (Bredmyran), Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502516</v>
+        <v>502004</v>
       </c>
       <c r="R7" t="n">
-        <v>6911753</v>
+        <v>6911976</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1383,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113660931</v>
+        <v>113661050</v>
       </c>
       <c r="B8" t="n">
-        <v>78247</v>
+        <v>57414</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1399,24 +1411,28 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1424,13 +1440,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502477</v>
+        <v>502516</v>
       </c>
       <c r="R8" t="n">
-        <v>6911601</v>
+        <v>6911753</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1496,10 +1512,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120000064</v>
+        <v>113660931</v>
       </c>
       <c r="B9" t="n">
-        <v>78279</v>
+        <v>78247</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1529,27 +1545,21 @@
           <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rörmyrberget, Mpd</t>
+          <t>Lomtjärnen (Lomtjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502560</v>
+        <v>502477</v>
       </c>
       <c r="R9" t="n">
-        <v>6911614</v>
+        <v>6911601</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1573,12 +1583,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-25</t>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-25</t>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,26 +1607,25 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>SCA SCA</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>SCA SCA</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120000096</v>
+        <v>120000064</v>
       </c>
       <c r="B10" t="n">
         <v>78279</v>
@@ -1644,11 +1663,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1657,10 +1672,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502537</v>
+        <v>502560</v>
       </c>
       <c r="R10" t="n">
-        <v>6911660</v>
+        <v>6911614</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1720,10 +1735,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120000128</v>
+        <v>120000096</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
+        <v>78279</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1732,30 +1747,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1764,7 +1779,6 @@
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1772,10 +1786,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502567</v>
+        <v>502537</v>
       </c>
       <c r="R11" t="n">
-        <v>6911635</v>
+        <v>6911660</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1835,10 +1849,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120000078</v>
+        <v>120000128</v>
       </c>
       <c r="B12" t="n">
-        <v>78279</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1847,34 +1861,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1882,10 +1901,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502534</v>
+        <v>502567</v>
       </c>
       <c r="R12" t="n">
-        <v>6911631</v>
+        <v>6911635</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1945,7 +1964,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120000048</v>
+        <v>120000078</v>
       </c>
       <c r="B13" t="n">
         <v>78279</v>
@@ -1992,10 +2011,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502578</v>
+        <v>502534</v>
       </c>
       <c r="R13" t="n">
-        <v>6911605</v>
+        <v>6911631</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2055,7 +2074,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120000023</v>
+        <v>120000048</v>
       </c>
       <c r="B14" t="n">
         <v>78279</v>
@@ -2102,10 +2121,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>502651</v>
+        <v>502578</v>
       </c>
       <c r="R14" t="n">
-        <v>6911576</v>
+        <v>6911605</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2162,6 +2181,116 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120000023</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78279</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Rörmyrberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>502651</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6911576</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-09-25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-09-25</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>SCA SCA</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>SCA SCA</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53456-2023 artfynd.xlsx
+++ b/artfynd/A 53456-2023 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>99037590</v>
       </c>
       <c r="B3" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 53456-2023 artfynd.xlsx
+++ b/artfynd/A 53456-2023 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>99037590</v>
       </c>
       <c r="B3" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,11 +815,6 @@
       </c>
       <c r="E3" t="n">
         <v>220787</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>

--- a/artfynd/A 53456-2023 artfynd.xlsx
+++ b/artfynd/A 53456-2023 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>99037590</v>
       </c>
       <c r="B3" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,6 +815,11 @@
       </c>
       <c r="E3" t="n">
         <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>

--- a/artfynd/A 53456-2023 artfynd.xlsx
+++ b/artfynd/A 53456-2023 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>99037590</v>
       </c>
       <c r="B3" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 53456-2023 artfynd.xlsx
+++ b/artfynd/A 53456-2023 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>99037590</v>
       </c>
       <c r="B3" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 53456-2023 artfynd.xlsx
+++ b/artfynd/A 53456-2023 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>99037590</v>
       </c>
       <c r="B3" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 53456-2023 artfynd.xlsx
+++ b/artfynd/A 53456-2023 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>99037590</v>
       </c>
       <c r="B3" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 53456-2023 artfynd.xlsx
+++ b/artfynd/A 53456-2023 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>99037590</v>
       </c>
       <c r="B3" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 53456-2023 artfynd.xlsx
+++ b/artfynd/A 53456-2023 artfynd.xlsx
@@ -1278,7 +1278,7 @@
         <v>113659639</v>
       </c>
       <c r="B7" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bredmyran (Bredmyran), Mpd</t>
+          <t>Bredmyran, Bredmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">

--- a/artfynd/A 53456-2023 artfynd.xlsx
+++ b/artfynd/A 53456-2023 artfynd.xlsx
@@ -1278,7 +1278,7 @@
         <v>113659639</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 53456-2023 artfynd.xlsx
+++ b/artfynd/A 53456-2023 artfynd.xlsx
@@ -1278,7 +1278,7 @@
         <v>113659639</v>
       </c>
       <c r="B7" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 53456-2023 artfynd.xlsx
+++ b/artfynd/A 53456-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101077322</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113660968</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113659639</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1101,6 +1121,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113660896</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1213,6 +1238,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113661050</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1321,6 +1351,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96619764</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1428,6 +1463,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101076821</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1535,6 +1575,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101076936</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1645,6 +1690,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120000128</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1755,6 +1805,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120000238</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1863,6 +1918,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113660931</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1968,6 +2028,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120000023</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2073,6 +2138,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120000048</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2178,6 +2248,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120000064</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2283,6 +2358,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120000078</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2392,8 +2472,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120000096</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>